--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Initiation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Initiation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rbb92c6df867e4ad4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R76b74988a20e40dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R73cc96c5b8c34cef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R148733a42900429e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R81e5528992a849c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R80e4a0eface64ffb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Re8ff9f0e2f5a4b73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R532a72d77e514bae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rcd501a42a9d24c77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R42c8d434cf3340bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R916626f6453a450d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rd26869a585be4f6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R6031f6438d1140e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R413ede7246214b35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R010af152fd294e28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="Re147aff075a34f31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R5b5238f9a1ae404c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf5510203f4cd40c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rf4d254457b204877"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rcbc03e7eefb2498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Re066994925584870"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R7a407d282b1e4f64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R88ba71a059614179"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Ra4d9732df2154b78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R39648a3783504520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rf1e4ec24007b4133"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R72b6495554e94b8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rae043b3dfdc74e34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R20d52920de784b71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R5dccbd879ec34489"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R054a27338c6c41cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rd3af4130ab464d87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R4e42a256192344a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rcc141a2221c04d45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rf6213436f6534a97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R687a34333f84444d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rddd649c6de874ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rfaeffd369a304cec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R7760d6bd6bfc40f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rd3567678a1f64a3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R8de42516e4164834"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rf29debfa328346f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rbd077d58a3b44375"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R411cbf9680c04425"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rac8dc242acd44331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rac00cf9a03aa4e4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R00bab44aca3b4a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R7e208be4e1134e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rf9ad293bfc7240be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R5b490e54600f45bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rfce833c6ec1f417a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R62c85ea7ca2045f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb98272990c024a9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rf2276997b9904eed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R5b9ba12688ee4443"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R9a5b20ebb4f04290"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>159</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>129</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$14,"Établi")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$7,"Défini")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
+        <x:f>COUNTIFS('Especes_factions'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D12" s="39" t="n">
-        <x:f>COUNTIFS('Especes_factions'!$C$7:$C$7,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Défini")</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="n">
+        <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
-        <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$14,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Défini")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$16,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$11)</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Défini")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$11,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Extrapolation")</x:f>
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$11,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$11,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$14,"P0")</x:f>
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$18)</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Défini")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$18,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Extrapolation")</x:f>
         <x:v>12</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$18,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$18,"P0")</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$14)</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Défini")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$14,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Établi")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$14,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$14,"P0")</x:f>
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>159</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>159</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>29</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>129</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>21</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4044,8 +4038,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4095,8 +4089,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4146,8 +4140,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4197,8 +4191,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Tous comportements et réglages de combat sont du design original.</x:v>
       </x:c>
     </x:row>
@@ -4234,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra440521e49d34091"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5de1326832914b68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4374,61 +4368,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4480,8 +4474,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4531,8 +4525,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4582,8 +4576,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4633,8 +4627,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4684,8 +4678,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4735,8 +4729,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -4786,8 +4780,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -4837,8 +4831,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -4872,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ca29e5b226a4eb7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcef5878109204c42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5012,61 +5006,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5118,8 +5112,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5169,8 +5163,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5220,8 +5214,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5271,8 +5265,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5322,8 +5316,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5373,8 +5367,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -5424,8 +5418,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -5475,8 +5469,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -5510,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb69213a0ae764775"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c5d98b914e41f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5650,61 +5644,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5756,8 +5750,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5807,8 +5801,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5858,8 +5852,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5909,8 +5903,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5960,8 +5954,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6011,8 +6005,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -6062,8 +6056,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -6113,8 +6107,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -6148,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9356d410febe4f7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae3528a637fe469d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6288,61 +6282,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6394,8 +6388,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6447,8 +6441,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6500,8 +6494,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6553,8 +6547,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6606,8 +6600,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6659,8 +6653,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6712,8 +6706,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6765,8 +6759,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6818,8 +6812,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str">
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6871,8 +6865,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str">
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str">
         <x:v>Sujet et intentions sont du design original, pas une transcription.</x:v>
       </x:c>
     </x:row>
@@ -6908,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eb9ec459a394b78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7998c28fd1054bf0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7048,61 +7042,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7154,8 +7148,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -7205,8 +7199,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -7256,8 +7250,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -7307,8 +7301,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -7358,8 +7352,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -7409,8 +7403,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -7460,8 +7454,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -7511,8 +7505,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -7546,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fc365cc4436484c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e61b9089ff14643"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7686,61 +7680,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7786,10 +7780,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INI-SRC-QUIET</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Quiet_Eddy</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -7825,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96e480f73d5a429e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56a12e4baee94d81"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7965,61 +7959,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8065,10 +8059,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8114,10 +8108,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INI-SRC-STORY</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8163,10 +8157,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8202,7 +8196,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3bb9b807084143b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R337083d94cd84cb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8342,61 +8336,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8442,10 +8436,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -8481,7 +8475,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60887cd8ec8c45e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85aa2c9b1c6241ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8621,61 +8615,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8725,8 +8719,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8774,8 +8768,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8823,8 +8817,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8872,8 +8866,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -8921,8 +8915,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -8970,8 +8964,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -9005,7 +8999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R772ad9481bde4515"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5abaf10960574715"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9145,61 +9139,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9245,10 +9239,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INI-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/555323/mass-effect-initiation-by-nk-jemisin/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9294,10 +9288,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INI-SRC-QUIET</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Quiet_Eddy</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -9333,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83a5fd3d56f34a3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2323fad3eec486f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9473,61 +9467,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9579,8 +9573,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9630,8 +9624,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9681,8 +9675,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9732,8 +9726,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -9767,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad87ad10cfc64a95"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ea8cef83e15405d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9907,61 +9901,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10013,8 +10007,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10064,8 +10058,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10115,8 +10109,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10166,8 +10160,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10217,8 +10211,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10268,8 +10262,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10319,8 +10313,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -10370,8 +10364,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -10421,8 +10415,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -10472,8 +10466,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -10507,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7630953f376e4b70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fe678e6c9934851"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10647,61 +10641,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10753,8 +10747,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10804,8 +10798,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10855,8 +10849,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10906,8 +10900,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10957,8 +10951,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -11008,8 +11002,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -11059,8 +11053,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="68" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -11110,8 +11104,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -11161,8 +11155,8 @@
       </x:c>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -11212,8 +11206,8 @@
       </x:c>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D16">
@@ -11247,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ecf06d646eb43f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb8650ba51e94c90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11387,61 +11381,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11493,8 +11487,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11544,8 +11538,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11595,8 +11589,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11646,8 +11640,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -11681,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63c02a13d7114816"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c2bf6ff11e646a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11821,61 +11815,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11925,8 +11919,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11974,8 +11968,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12023,8 +12017,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12072,8 +12066,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12121,8 +12115,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D11">
@@ -12156,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf15e41fdaa684bbf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9648514aa75f46b6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12296,61 +12290,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12400,8 +12394,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12449,8 +12443,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="44" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12498,8 +12492,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="44" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12547,8 +12541,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12596,8 +12590,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="44" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12645,8 +12639,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12694,8 +12688,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12743,8 +12737,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -12778,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb62289cc7eeb44c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec748404d4f046c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12918,61 +12912,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13024,8 +13018,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -13075,8 +13069,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -13126,8 +13120,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -13177,8 +13171,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="44" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -13228,8 +13222,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -13279,8 +13273,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -13330,8 +13324,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -13381,8 +13375,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="68" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -13424,8 +13418,8 @@
       <x:c r="O15" s="9" t="str"/>
       <x:c r="P15" s="9" t="str"/>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
     <x:row r="16" ht="68" customHeight="1">
       <x:c r="A16" s="19" t="str">
@@ -13467,8 +13461,8 @@
       <x:c r="O16" s="7" t="str"/>
       <x:c r="P16" s="7" t="str"/>
       <x:c r="Q16" s="7" t="str"/>
-      <x:c r="R16" s="21" t="str"/>
-      <x:c r="S16" s="21" t="str"/>
+      <x:c r="R16" s="7" t="str"/>
+      <x:c r="S16" s="7" t="str"/>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="18" t="str">
@@ -13510,8 +13504,8 @@
       <x:c r="O17" s="9" t="str"/>
       <x:c r="P17" s="9" t="str"/>
       <x:c r="Q17" s="9" t="str"/>
-      <x:c r="R17" s="20" t="str"/>
-      <x:c r="S17" s="20" t="str"/>
+      <x:c r="R17" s="9" t="str"/>
+      <x:c r="S17" s="9" t="str"/>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="19" t="str">
@@ -13553,8 +13547,8 @@
       <x:c r="O18" s="7" t="str"/>
       <x:c r="P18" s="7" t="str"/>
       <x:c r="Q18" s="7" t="str"/>
-      <x:c r="R18" s="21" t="str"/>
-      <x:c r="S18" s="21" t="str"/>
+      <x:c r="R18" s="7" t="str"/>
+      <x:c r="S18" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D18">
@@ -13588,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7164bec1f1f740ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9731087d3f544b10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13728,61 +13722,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -13828,10 +13822,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INI-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/555323/mass-effect-initiation-by-nk-jemisin/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13877,10 +13871,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INI-SRC-PUB</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/555323/mass-effect-initiation-by-nk-jemisin/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13926,10 +13920,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -13975,10 +13969,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14024,10 +14018,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14073,10 +14067,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>INI-SRC-MEDEA</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Medea</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14120,8 +14114,8 @@
         <x:v>Limite de continuité / contrôle transversal</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14167,10 +14161,10 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="S14" s="7" t="str">
         <x:v>Aucun numéro de chapitre ou de page n’est attribué sans exemplaire vérifié.</x:v>
       </x:c>
     </x:row>
@@ -14206,7 +14200,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7aa3ab392e5e4b1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9d3aea92bac47b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14271,10 +14265,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -14323,7 +14317,7 @@
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Cora, SAM-E et la récupération d’une technologie volée ; adaptation originale mêlant infiltration, coopération humain/IA et évacuation de civils.</x:v>
+        <x:v>159 fiches de production ; 5 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -14342,11 +14336,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -14499,22 +14493,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -14723,13 +14717,13 @@
       <x:c r="F38" s="2"/>
     </x:row>
     <x:row r="39" ht="34" customHeight="1">
-      <x:c r="A39" s="30" t="str">
+      <x:c r="A39" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B39" s="31" t="str">
+      <x:c r="B39" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C39" s="32" t="str">
+      <x:c r="C39" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D39" s="2"/>
@@ -14806,10 +14800,16 @@
       <x:c r="E44" s="2"/>
       <x:c r="F44" s="2"/>
     </x:row>
-    <x:row r="45" ht="22" customHeight="1">
-      <x:c r="A45" s="2"/>
-      <x:c r="B45" s="2"/>
-      <x:c r="C45" s="2"/>
+    <x:row r="45" ht="96" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>Complément pouvoirs, modules et lectures</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>0 fiches de pouvoirs utilisées, 0 familles de modules préparables et 5 références consultables dans une lecture documentaire. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>Arbres et progression complets, modèles et rangs exacts, campagnes et dialogues intégraux, niveaux et ressources visuelles propres à l’œuvre restent à réaliser ou vérifier. Les références lues ne rendent pas leurs personnages jouables.</x:v>
+      </x:c>
       <x:c r="D45" s="2"/>
       <x:c r="E45" s="2"/>
       <x:c r="F45" s="2"/>
@@ -15365,6 +15365,14 @@
       <x:c r="D114" s="2"/>
       <x:c r="E114" s="2"/>
       <x:c r="F114" s="2"/>
+    </x:row>
+    <x:row r="115" ht="22" customHeight="1">
+      <x:c r="A115" s="2"/>
+      <x:c r="B115" s="2"/>
+      <x:c r="C115" s="2"/>
+      <x:c r="D115" s="2"/>
+      <x:c r="E115" s="2"/>
+      <x:c r="F115" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15506,61 +15514,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15606,10 +15614,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15655,10 +15663,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15704,10 +15712,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INI-SRC-REVIEW</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://reactormag.com/book-reviews-mass-effect-initiation-by-n-k-jemisin-and-mac-walters-a-review//</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15753,10 +15761,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>INI-SRC-MEDEA</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Medea</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15802,10 +15810,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>INI-SRC-VLASSIA</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Vlassia_Ariokis</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15851,10 +15859,10 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>INI-SRC-QUIET</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Quiet_Eddy</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15900,10 +15908,10 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>INI-SRC-QUIET</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Quiet_Eddy</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="S13" s="9" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15949,10 +15957,10 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>INI-SRC-QUIET</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Quiet_Eddy</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="S14" s="7" t="str">
         <x:v>Le costume proposé dans les fiches de production n’est pas un modèle officiel.</x:v>
       </x:c>
     </x:row>
@@ -15988,7 +15996,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8280f2e8e7654cb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R015e2ca881904f5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16015,7 +16023,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16128,65 +16136,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="68" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>INI-REF-AUGMENTS</x:v>
       </x:c>
@@ -16194,7 +16202,7 @@
         <x:v>Augments de Quiet Eddy</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16213,7 +16221,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.ini.augments ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire INI-REF-AUGMENTS consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>L’action reste dans la Voie lactée avant le départ des arches. SAM-E ne devient pas un compagnon durable disponible dans Andromeda ; préserver les limites et conséquences de son lien avec Cora.</x:v>
@@ -16228,11 +16236,11 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INI-SRC-MEDEA</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Medea</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16267,7 +16275,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcddb35dd4af4112"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54709371929b434c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16294,7 +16302,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="69" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="255" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -16407,65 +16415,65 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="68" customHeight="1">
+    <x:row r="7" ht="82" customHeight="1">
       <x:c r="A7" s="18" t="str">
         <x:v>INI-REF-THEIA</x:v>
       </x:c>
@@ -16473,7 +16481,7 @@
         <x:v>Station Theia</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D7" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16492,7 +16500,7 @@
       <x:c r="J7" s="9" t="str"/>
       <x:c r="K7" s="9" t="str"/>
       <x:c r="L7" s="9" t="str">
-        <x:v>Codex ref.ini.theia ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire INI-REF-THEIA consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M7" s="9" t="str">
         <x:v>L’action reste dans la Voie lactée avant le départ des arches. SAM-E ne devient pas un compagnon durable disponible dans Andromeda ; préserver les limites et conséquences de son lien avec Cora.</x:v>
@@ -16507,14 +16515,14 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INI-SRC-STORY</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="68" customHeight="1">
+      <x:c r="S7" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="82" customHeight="1">
       <x:c r="A8" s="19" t="str">
         <x:v>INI-REF-HOMEAWAY</x:v>
       </x:c>
@@ -16522,7 +16530,7 @@
         <x:v>Home Away</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D8" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16541,7 +16549,7 @@
       <x:c r="J8" s="7" t="str"/>
       <x:c r="K8" s="7" t="str"/>
       <x:c r="L8" s="7" t="str">
-        <x:v>Codex ref.ini.homeaway ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire INI-REF-HOMEAWAY consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M8" s="7" t="str">
         <x:v>L’action reste dans la Voie lactée avant le départ des arches. SAM-E ne devient pas un compagnon durable disponible dans Andromeda ; préserver les limites et conséquences de son lien avec Cora.</x:v>
@@ -16556,14 +16564,14 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INI-SRC-STORY</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Storyline_IV</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="68" customHeight="1">
+      <x:c r="S8" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
         <x:v>INI-REF-ILLIUM</x:v>
       </x:c>
@@ -16571,7 +16579,7 @@
         <x:v>Illium</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D9" s="16" t="str">
         <x:v>Établi</x:v>
@@ -16590,7 +16598,7 @@
       <x:c r="J9" s="9" t="str"/>
       <x:c r="K9" s="9" t="str"/>
       <x:c r="L9" s="9" t="str">
-        <x:v>Codex ref.ini.illium ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire INI-REF-ILLIUM consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M9" s="9" t="str">
         <x:v>L’action reste dans la Voie lactée avant le départ des arches. SAM-E ne devient pas un compagnon durable disponible dans Andromeda ; préserver les limites et conséquences de son lien avec Cora.</x:v>
@@ -16605,14 +16613,14 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="68" customHeight="1">
+      <x:c r="S9" s="9" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
         <x:v>INI-REF-QUIET</x:v>
       </x:c>
@@ -16620,7 +16628,7 @@
         <x:v>Quiet Eddy</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D10" s="17" t="str">
         <x:v>Établi</x:v>
@@ -16639,7 +16647,7 @@
       <x:c r="J10" s="7" t="str"/>
       <x:c r="K10" s="7" t="str"/>
       <x:c r="L10" s="7" t="str">
-        <x:v>Codex ref.ini.quiet ; affichage bref avec source.</x:v>
+        <x:v>Référence documentaire INI-REF-QUIET consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M10" s="7" t="str">
         <x:v>L’action reste dans la Voie lactée avant le départ des arches. SAM-E ne devient pas un compagnon durable disponible dans Andromeda ; préserver les limites et conséquences de son lien avec Cora.</x:v>
@@ -16654,11 +16662,11 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>INI-SRC-QUIET</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Quiet_Eddy</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
-        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
+      <x:c r="S10" s="7" t="str">
+        <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -16693,7 +16701,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4633a588eedc4f53"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89f5064cb850461c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16833,61 +16841,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16937,8 +16945,8 @@
       <x:c r="O7" s="9" t="str"/>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -16988,8 +16996,8 @@
       <x:c r="O8" s="7" t="str"/>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17039,8 +17047,8 @@
       <x:c r="O9" s="9" t="str"/>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17090,8 +17098,8 @@
       <x:c r="O10" s="7" t="str"/>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17141,8 +17149,8 @@
       <x:c r="O11" s="9" t="str"/>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17192,8 +17200,8 @@
       <x:c r="O12" s="7" t="str"/>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17243,8 +17251,8 @@
       <x:c r="O13" s="9" t="str"/>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17294,8 +17302,8 @@
       <x:c r="O14" s="7" t="str"/>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Dimensions, connexions et accessoires de cette carte sont des propositions originales.</x:v>
       </x:c>
     </x:row>
@@ -17331,7 +17339,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf56476b4c678464f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R974a23cbb83347a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17471,61 +17479,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17577,8 +17585,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17630,8 +17638,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17683,8 +17691,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17736,8 +17744,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17789,8 +17797,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17842,8 +17850,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17895,8 +17903,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str">
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17948,8 +17956,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str">
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str">
         <x:v>Boucle de parcours de production ; la dernière liaison sert à la consultation post-module, pas à remonter le temps.</x:v>
       </x:c>
     </x:row>
@@ -17985,7 +17993,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde913ba7896a4d69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R191f63bfda8443ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18125,61 +18133,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18231,8 +18239,8 @@
       </x:c>
       <x:c r="P7" s="9" t="str"/>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -18282,8 +18290,8 @@
       </x:c>
       <x:c r="P8" s="7" t="str"/>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -18333,8 +18341,8 @@
       </x:c>
       <x:c r="P9" s="9" t="str"/>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -18384,8 +18392,8 @@
       </x:c>
       <x:c r="P10" s="7" t="str"/>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -18435,8 +18443,8 @@
       </x:c>
       <x:c r="P11" s="9" t="str"/>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -18486,8 +18494,8 @@
       </x:c>
       <x:c r="P12" s="7" t="str"/>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -18537,8 +18545,8 @@
       </x:c>
       <x:c r="P13" s="9" t="str"/>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -18588,8 +18596,8 @@
       </x:c>
       <x:c r="P14" s="7" t="str"/>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D14">
@@ -18623,7 +18631,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d36ba5dd75b4377"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73a1141b2ed9479a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18763,61 +18771,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -18863,10 +18871,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>INI-SRC-SAME</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/SAM-E</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18912,10 +18920,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>INI-SRC-QUIET</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Quiet_Eddy</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Ce relevé n’est ni un inventaire exhaustif ni un résumé scène par scène.</x:v>
       </x:c>
     </x:row>
@@ -18951,7 +18959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaef1d1dd0004638"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b01cbf58f2b486b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Initiation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Initiation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R20d52920de784b71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R5dccbd879ec34489"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R054a27338c6c41cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rd3af4130ab464d87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R4e42a256192344a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rcc141a2221c04d45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rf6213436f6534a97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R687a34333f84444d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rddd649c6de874ee4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rfaeffd369a304cec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R7760d6bd6bfc40f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rd3567678a1f64a3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R8de42516e4164834"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rf29debfa328346f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rbd077d58a3b44375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R411cbf9680c04425"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rac8dc242acd44331"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rac00cf9a03aa4e4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R00bab44aca3b4a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R7e208be4e1134e12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rf9ad293bfc7240be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R5b490e54600f45bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="Rfce833c6ec1f417a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R62c85ea7ca2045f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rb98272990c024a9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rf2276997b9904eed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R5b9ba12688ee4443"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R9a5b20ebb4f04290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1caaa9cbfa2f4d72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rf7db515bb79c410a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rdbfbfc09368e4be6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R06a408e9155d4cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R9f8fdb5fb56f470f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R4415b69a969d4f2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Ra44099a8fe4a447b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rc429e442619c4ba8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rd5b61ae13f2448a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R7bd0f4f431354c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rc7742fc5d0de43ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re6ef8001739449bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R4d0a2d7060c14ed8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R67b3f2c9e0334656"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rce8fd9409850448b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R90d0ddbbee5d466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R89a75deee0bc49f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Reb58f191903d48b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R67cebd0a62664f62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rcfd47c1e0e92413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R067606e6b29b44b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R468937af221c45f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R0850c135566d4993"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R5aed4fe2ced3438e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R4f0abe207c604b6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R7d3a6428f9994d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R7790673e45ff48b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rf9cb261f222b4f2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5de1326832914b68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb424df2f43564667"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcef5878109204c42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb81835a1c2084818"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70c5d98b914e41f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70d6744af5ba496c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae3528a637fe469d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca3fcdcbe65c41e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7998c28fd1054bf0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra55614c0e8974a03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e61b9089ff14643"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c3b0ebde5b94547"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56a12e4baee94d81"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1d26ffd2fc14632"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8196,7 +8196,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R337083d94cd84cb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc6c7940de744b0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8475,7 +8475,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85aa2c9b1c6241ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb59428496fad4e17"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8999,7 +8999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5abaf10960574715"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re363ce0d84f540be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9327,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2323fad3eec486f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd65013a57c76484f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9761,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ea8cef83e15405d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radcd28211696410e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10501,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fe678e6c9934851"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37fc622a080e4029"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11241,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb8650ba51e94c90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra845ca03368d475d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11675,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c2bf6ff11e646a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3e779941bcc421d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12150,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9648514aa75f46b6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49d154e075ea410a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12772,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec748404d4f046c6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88a73622e6f44a84"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13582,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9731087d3f544b10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbccb7022f854d3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14200,7 +14200,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9d3aea92bac47b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3648ef004a68459e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15996,7 +15996,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R015e2ca881904f5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43ee425a1aaf4d1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16275,7 +16275,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54709371929b434c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeb8c312945949d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16701,7 +16701,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89f5064cb850461c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7524b45c102a4826"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17339,7 +17339,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R974a23cbb83347a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a0241ef09634cc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17993,7 +17993,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R191f63bfda8443ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c31026604da4897"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18631,7 +18631,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73a1141b2ed9479a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2b52ae7116b44d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18959,7 +18959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b01cbf58f2b486b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbdb5560bae5411e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Initiation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Initiation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R1caaa9cbfa2f4d72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Rf7db515bb79c410a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rdbfbfc09368e4be6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R06a408e9155d4cdf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R9f8fdb5fb56f470f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R4415b69a969d4f2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Ra44099a8fe4a447b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rc429e442619c4ba8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rd5b61ae13f2448a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R7bd0f4f431354c9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rc7742fc5d0de43ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re6ef8001739449bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R4d0a2d7060c14ed8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R67b3f2c9e0334656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rce8fd9409850448b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R90d0ddbbee5d466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R89a75deee0bc49f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Reb58f191903d48b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R67cebd0a62664f62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rcfd47c1e0e92413f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R067606e6b29b44b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R468937af221c45f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R0850c135566d4993"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R5aed4fe2ced3438e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R4f0abe207c604b6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R7d3a6428f9994d25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R7790673e45ff48b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rf9cb261f222b4f2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rcab71f38f0e0437b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Ra6cd0886f5dc4d95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rcf18c60db9a144ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R51534707bbf449b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R767f054240b4459d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R2bb492ab5460452c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rd43608806000413f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R771bc13d13934435"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rd0f55eef2f114a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R1c680a9624934bbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R75fad2f38d8f42f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R7c1952843d4f4db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R1539a591009e4ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rff8c995a25c3428f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rcb3176d92ad940e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R03bd3d0fc2b5403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R7e1189d30f654682"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Red8fae4d75024319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R3bd1d742eec04e59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R76e77fe4d7f74bf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rae4e1ae4313c46c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rdba4716d7385455f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R95463121f3eb429a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R9d03c0f10cd64981"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R3d49f62c98ca4a0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rdfb33a652b0a45cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R3f1ea0612fd140aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rb56c89775b85428a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb424df2f43564667"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56720f6b157f4b60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb81835a1c2084818"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3212b2a287a452f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70d6744af5ba496c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4f6bec2cf894e83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca3fcdcbe65c41e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b152cc362974f58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra55614c0e8974a03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d378e8cbd544a9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c3b0ebde5b94547"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e61e8a9ccdf4e15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1d26ffd2fc14632"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0c61e84f7d64a42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8196,7 +8196,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc6c7940de744b0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26d962fd783d4a6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8475,7 +8475,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb59428496fad4e17"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re13cf7cab3044fe5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8999,7 +8999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re363ce0d84f540be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra25a10b6a4c943bc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9327,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd65013a57c76484f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46d925286bca4b38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9761,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radcd28211696410e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35d83fecf0b54f25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10501,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37fc622a080e4029"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e13354e5cfb46ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11241,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra845ca03368d475d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3fa7070e4014223"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11675,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3e779941bcc421d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49362e680bb04f12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12150,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49d154e075ea410a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R772219632c6f4e4b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12772,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88a73622e6f44a84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e0562e5ba174a79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13582,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbccb7022f854d3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaf6b060b3a44ac4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14200,7 +14200,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3648ef004a68459e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R253c89ba87f44ade"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15996,7 +15996,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43ee425a1aaf4d1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dd70186dbca4841"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16275,7 +16275,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeb8c312945949d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58f24b38b6304f0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16701,7 +16701,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7524b45c102a4826"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c76da03f6534bb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17339,7 +17339,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a0241ef09634cc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3823eafc8e074644"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17993,7 +17993,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c31026604da4897"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74b738ba454b4a76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18631,7 +18631,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2b52ae7116b44d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3597e36fd64d4116"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18959,7 +18959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbbdb5560bae5411e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0da935772494cc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Initiation_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Andromeda_Initiation_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rcab71f38f0e0437b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="Ra6cd0886f5dc4d95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rcf18c60db9a144ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R51534707bbf449b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R767f054240b4459d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R2bb492ab5460452c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rd43608806000413f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R771bc13d13934435"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rd0f55eef2f114a51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R1c680a9624934bbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R75fad2f38d8f42f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R7c1952843d4f4db8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R1539a591009e4ac9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rff8c995a25c3428f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Rcb3176d92ad940e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R03bd3d0fc2b5403b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R7e1189d30f654682"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Red8fae4d75024319"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R3bd1d742eec04e59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R76e77fe4d7f74bf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Rae4e1ae4313c46c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Rdba4716d7385455f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R95463121f3eb429a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R9d03c0f10cd64981"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R3d49f62c98ca4a0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rdfb33a652b0a45cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R3f1ea0612fd140aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="Rb56c89775b85428a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R024c393674214c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R4a4b28da05ce44e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R6277cccf4b6b40d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R5a3767f3bd574c3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Re0a8b874467343a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R261e955d6f5b47b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R0f1f4576a53d4945"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R0c7d6bf2bf0f4b8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R323c26f46ddb436f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R022ee59372ff465c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rbfe3ab2aa81a4353"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Rf67206cd4ea04e61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Ref058b3204144cc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R1b5ea5d32aa34536"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R914492807c674bb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R5413e075cee44a22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R8950e557fb8b49cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R9513dce9591f4ae3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R815f556102cc47a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R564a94386d4e4629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Ra9c181febcd84db3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R69220277648c4239"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R13839c5a6d9a4941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R22daaa3a8aad45b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R177981477a9b4e7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rf9e845d63013410d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rb40212b1bc0e452f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R13e0cffe439846b8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4228,7 +4228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56720f6b157f4b60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd44feec065d742fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4866,7 +4866,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3212b2a287a452f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70637bc1f2f84a78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5504,7 +5504,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4f6bec2cf894e83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a5f182b730d4c06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6142,7 +6142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b152cc362974f58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf20677c02b884fa9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6902,7 +6902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d378e8cbd544a9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb84dfad32cd5447b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7540,7 +7540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e61e8a9ccdf4e15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7e8edd904d34905"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7819,7 +7819,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0c61e84f7d64a42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34187747c6ac4eda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8196,7 +8196,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26d962fd783d4a6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33a08a87ede34411"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8475,7 +8475,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re13cf7cab3044fe5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bc867805e004f1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8999,7 +8999,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra25a10b6a4c943bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c6e50a740e140dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9327,7 +9327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46d925286bca4b38"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fe7959e74da4c25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9761,7 +9761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35d83fecf0b54f25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae7a2e8b8c8e4d68"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10501,7 +10501,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e13354e5cfb46ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe0f682f928c444c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11241,7 +11241,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3fa7070e4014223"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd50cf35b3f748e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11675,7 +11675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49362e680bb04f12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd16513718ece4b29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12150,7 +12150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R772219632c6f4e4b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf885d0b3cbf4cca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12772,7 +12772,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e0562e5ba174a79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a0eb95af1b548f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13582,7 +13582,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raaf6b060b3a44ac4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03970b251db0495f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14200,7 +14200,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R253c89ba87f44ade"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a060e4876ad4201"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15996,7 +15996,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dd70186dbca4841"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0dab2d71b34d4dab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16275,7 +16275,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58f24b38b6304f0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31a0474daf8242c8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16701,7 +16701,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c76da03f6534bb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3d7c6b5b209431d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17339,7 +17339,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3823eafc8e074644"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda14907b0c1e4480"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17993,7 +17993,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74b738ba454b4a76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc21a8b2b02a94765"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18631,7 +18631,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3597e36fd64d4116"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f2bc637af254d74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18959,7 +18959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0da935772494cc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb66843f5393d40ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>